--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6148-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6148-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0ED3ACE-57E1-4A59-ACC6-CC5E668200FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7A2C10A-5383-4FD3-81D9-C737EEEBB130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{4E15E093-6690-46D6-8900-66081D6D273C}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{64BE4202-AC31-4D3F-BCDB-9954CBED13C7}"/>
   </bookViews>
   <sheets>
     <sheet name="6148-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1511,25 +1511,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB7E765-0357-4292-BDE1-DC195569B3C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236D7E0E-0716-4390-B99C-393E8EE62322}">
   <dimension ref="A1:R61"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1557,7 +1557,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1587,7 +1587,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1683,7 +1683,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2026</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <v>2025</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>26</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>26</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="38">
         <v>2024</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2405,7 +2405,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="40">
         <v>2023</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>26</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>26</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>26</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>26</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="38">
         <v>2022</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>26</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>26</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="40">
         <v>2021</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>26</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>26</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>26</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>26</v>
       </c>
@@ -3407,7 +3407,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="38">
         <v>2020</v>
       </c>
@@ -3461,7 +3461,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>26</v>
       </c>
@@ -3517,7 +3517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>26</v>
       </c>
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>26</v>
       </c>
@@ -3629,7 +3629,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="40">
         <v>2019</v>
       </c>
@@ -3683,7 +3683,7 @@
         <v>7.84</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="38">
         <v>2018</v>
       </c>
@@ -3737,7 +3737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="40">
         <v>2017</v>
       </c>
@@ -3791,7 +3791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="38">
         <v>2016</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="40">
         <v>2015</v>
       </c>
@@ -3899,7 +3899,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="38">
         <v>2014</v>
       </c>
@@ -3953,7 +3953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="40">
         <v>2013</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="38">
         <v>2012</v>
       </c>
@@ -4061,7 +4061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="40">
         <v>2011</v>
       </c>
@@ -4115,7 +4115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="38">
         <v>2010</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="40">
         <v>2009</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="38">
         <v>2008</v>
       </c>
@@ -4277,7 +4277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="40">
         <v>2007</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="38">
         <v>2006</v>
       </c>
@@ -4385,7 +4385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="40">
         <v>2005</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="38">
         <v>2004</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="40">
         <v>2003</v>
       </c>
@@ -4547,7 +4547,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="38">
         <v>2002</v>
       </c>
@@ -4601,7 +4601,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="40">
         <v>2001</v>
       </c>
@@ -4655,7 +4655,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="38">
         <v>2000</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="40">
         <v>1999</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="38" t="s">
         <v>55</v>
       </c>
